--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/58.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/58.xlsx
@@ -426,13 +426,13 @@
         <v>-22.39280449574329</v>
       </c>
       <c r="E2">
-        <v>-11.79905431554291</v>
+        <v>-18.7388637482396</v>
       </c>
       <c r="F2">
-        <v>2.65772305911819</v>
+        <v>1.233159755706213</v>
       </c>
       <c r="G2">
-        <v>-16.33422125452298</v>
+        <v>-18.0466555587124</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.21814707164253</v>
       </c>
       <c r="E3">
-        <v>-13.07208987163119</v>
+        <v>-19.82011390162903</v>
       </c>
       <c r="F3">
-        <v>2.514665665389521</v>
+        <v>1.074903476870978</v>
       </c>
       <c r="G3">
-        <v>-16.26682847898004</v>
+        <v>-16.96753523727664</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.0090829466727</v>
       </c>
       <c r="E4">
-        <v>-11.27460268376659</v>
+        <v>-20.62493241616824</v>
       </c>
       <c r="F4">
-        <v>2.174650667766824</v>
+        <v>1.499073975678882</v>
       </c>
       <c r="G4">
-        <v>-16.51879575524674</v>
+        <v>-16.83887585071117</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.76320586166484</v>
       </c>
       <c r="E5">
-        <v>-13.5014254353504</v>
+        <v>-20.92356716307807</v>
       </c>
       <c r="F5">
-        <v>2.467360916485252</v>
+        <v>1.449567426217972</v>
       </c>
       <c r="G5">
-        <v>-15.68729430851184</v>
+        <v>-16.97791048699672</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.47886326365847</v>
       </c>
       <c r="E6">
-        <v>-13.46410628105319</v>
+        <v>-21.42357409216098</v>
       </c>
       <c r="F6">
-        <v>2.830233884220798</v>
+        <v>1.496433140398757</v>
       </c>
       <c r="G6">
-        <v>-13.91067018158873</v>
+        <v>-16.6778575367721</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.163274530416</v>
       </c>
       <c r="E7">
-        <v>-14.96101600665866</v>
+        <v>-21.01773678006757</v>
       </c>
       <c r="F7">
-        <v>2.626513488850315</v>
+        <v>1.573963359096374</v>
       </c>
       <c r="G7">
-        <v>-14.2833482245811</v>
+        <v>-15.94667389624097</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.80076695496276</v>
       </c>
       <c r="E8">
-        <v>-15.3609663025421</v>
+        <v>-22.53908215141844</v>
       </c>
       <c r="F8">
-        <v>2.767816400419855</v>
+        <v>1.628968611377067</v>
       </c>
       <c r="G8">
-        <v>-13.29258967413402</v>
+        <v>-15.5661730341393</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.40111279310623</v>
       </c>
       <c r="E9">
-        <v>-14.37463296435344</v>
+        <v>-22.44332304005224</v>
       </c>
       <c r="F9">
-        <v>3.019805764351465</v>
+        <v>1.712666853755929</v>
       </c>
       <c r="G9">
-        <v>-11.69383122739933</v>
+        <v>-15.41784238597948</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.99542207426902</v>
       </c>
       <c r="E10">
-        <v>-15.33072968159288</v>
+        <v>-22.87047135082575</v>
       </c>
       <c r="F10">
-        <v>3.053684334391159</v>
+        <v>1.803066588423439</v>
       </c>
       <c r="G10">
-        <v>-11.98006099472472</v>
+        <v>-14.42557091622096</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.60729490792206</v>
       </c>
       <c r="E11">
-        <v>-15.64412725376772</v>
+        <v>-23.52080550306729</v>
       </c>
       <c r="F11">
-        <v>3.413046681073641</v>
+        <v>2.091552163387589</v>
       </c>
       <c r="G11">
-        <v>-10.82136012434318</v>
+        <v>-13.91040037212727</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.25125812602764</v>
       </c>
       <c r="E12">
-        <v>-17.80161001134608</v>
+        <v>-24.57113070745833</v>
       </c>
       <c r="F12">
-        <v>4.021731048650717</v>
+        <v>2.218583961341699</v>
       </c>
       <c r="G12">
-        <v>-11.30435878688623</v>
+        <v>-13.54599869298308</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.95421379140148</v>
       </c>
       <c r="E13">
-        <v>-16.14135822828393</v>
+        <v>-25.16272602334638</v>
       </c>
       <c r="F13">
-        <v>4.02176749681644</v>
+        <v>2.305835899878571</v>
       </c>
       <c r="G13">
-        <v>-11.33412721237536</v>
+        <v>-13.1454425460045</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.76219774356002</v>
       </c>
       <c r="E14">
-        <v>-19.14683850006463</v>
+        <v>-25.17068708065187</v>
       </c>
       <c r="F14">
-        <v>4.132376082642647</v>
+        <v>2.611617786213175</v>
       </c>
       <c r="G14">
-        <v>-10.09136496966065</v>
+        <v>-12.96137621402102</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.68368987889822</v>
       </c>
       <c r="E15">
-        <v>-21.94593356894576</v>
+        <v>-26.72175735538908</v>
       </c>
       <c r="F15">
-        <v>4.944325243518667</v>
+        <v>3.085709018183388</v>
       </c>
       <c r="G15">
-        <v>-10.18201101707144</v>
+        <v>-12.01390801231823</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.71578374325954</v>
       </c>
       <c r="E16">
-        <v>-21.66671239010681</v>
+        <v>-27.03651799824022</v>
       </c>
       <c r="F16">
-        <v>4.837207397927857</v>
+        <v>2.991440807744804</v>
       </c>
       <c r="G16">
-        <v>-9.007306969553065</v>
+        <v>-11.84818872371339</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.85840904652797</v>
       </c>
       <c r="E17">
-        <v>-21.36216345614296</v>
+        <v>-27.99093012314881</v>
       </c>
       <c r="F17">
-        <v>5.635867888928167</v>
+        <v>3.313896073162956</v>
       </c>
       <c r="G17">
-        <v>-9.401079808721677</v>
+        <v>-11.5068019571582</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-19.10869615869753</v>
       </c>
       <c r="E18">
-        <v>-23.43295763579249</v>
+        <v>-28.8224213495932</v>
       </c>
       <c r="F18">
-        <v>5.808254458920355</v>
+        <v>3.455344777395389</v>
       </c>
       <c r="G18">
-        <v>-9.586874245476654</v>
+        <v>-11.04782461304811</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-19.42695842870627</v>
       </c>
       <c r="E19">
-        <v>-22.67262232143063</v>
+        <v>-29.32439363639544</v>
       </c>
       <c r="F19">
-        <v>5.775605186106415</v>
+        <v>3.726654982629894</v>
       </c>
       <c r="G19">
-        <v>-8.403953423929813</v>
+        <v>-11.0793939753106</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-19.78118350720732</v>
       </c>
       <c r="E20">
-        <v>-24.36407076193161</v>
+        <v>-29.9718476791681</v>
       </c>
       <c r="F20">
-        <v>5.703285398372407</v>
+        <v>3.921664266392537</v>
       </c>
       <c r="G20">
-        <v>-9.442286169048986</v>
+        <v>-10.94060266412219</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-20.15145455483089</v>
       </c>
       <c r="E21">
-        <v>-25.38410500368535</v>
+        <v>-30.14209792372347</v>
       </c>
       <c r="F21">
-        <v>6.218407324538085</v>
+        <v>4.064209729066276</v>
       </c>
       <c r="G21">
-        <v>-8.986215483922368</v>
+        <v>-10.25837868157134</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-20.51450385624768</v>
       </c>
       <c r="E22">
-        <v>-25.51933429450241</v>
+        <v>-30.48716311463394</v>
       </c>
       <c r="F22">
-        <v>5.871162336223755</v>
+        <v>4.13909082880974</v>
       </c>
       <c r="G22">
-        <v>-7.954046974597319</v>
+        <v>-10.64998311341173</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-20.82623481936353</v>
       </c>
       <c r="E23">
-        <v>-27.8802270475573</v>
+        <v>-32.08964515478024</v>
       </c>
       <c r="F23">
-        <v>5.934295529460717</v>
+        <v>4.467220410937069</v>
       </c>
       <c r="G23">
-        <v>-7.334028142729376</v>
+        <v>-10.50043583976623</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-21.06481677348744</v>
       </c>
       <c r="E24">
-        <v>-26.00504483114311</v>
+        <v>-31.91446340203051</v>
       </c>
       <c r="F24">
-        <v>6.254027122858465</v>
+        <v>4.20594007821566</v>
       </c>
       <c r="G24">
-        <v>-7.817516766012236</v>
+        <v>-9.987370802635526</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-21.22589285688297</v>
       </c>
       <c r="E25">
-        <v>-27.46478937056763</v>
+        <v>-31.19860675937199</v>
       </c>
       <c r="F25">
-        <v>5.975226819567846</v>
+        <v>4.354020691874905</v>
       </c>
       <c r="G25">
-        <v>-7.939023718940107</v>
+        <v>-10.41455035684092</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-21.29668080579839</v>
       </c>
       <c r="E26">
-        <v>-25.19390003841518</v>
+        <v>-32.73098349340554</v>
       </c>
       <c r="F26">
-        <v>6.037468689479395</v>
+        <v>3.9903607751067</v>
       </c>
       <c r="G26">
-        <v>-8.435155315637443</v>
+        <v>-10.2922720468024</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-21.26251248286187</v>
       </c>
       <c r="E27">
-        <v>-26.53933683693809</v>
+        <v>-31.51176432242442</v>
       </c>
       <c r="F27">
-        <v>6.057074489168854</v>
+        <v>4.059484721400707</v>
       </c>
       <c r="G27">
-        <v>-8.423336668062246</v>
+        <v>-9.759323873162829</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-21.12665457322358</v>
       </c>
       <c r="E28">
-        <v>-26.88492733083346</v>
+        <v>-32.09912325087829</v>
       </c>
       <c r="F28">
-        <v>5.666061880760209</v>
+        <v>4.111822630644386</v>
       </c>
       <c r="G28">
-        <v>-7.558843979755743</v>
+        <v>-10.04647728269367</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-20.91564501430071</v>
       </c>
       <c r="E29">
-        <v>-25.80177521836081</v>
+        <v>-32.14214148971416</v>
       </c>
       <c r="F29">
-        <v>5.427705787543873</v>
+        <v>3.881011307732749</v>
       </c>
       <c r="G29">
-        <v>-7.995839301485079</v>
+        <v>-10.34310547355791</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-20.63628655533475</v>
       </c>
       <c r="E30">
-        <v>-24.99389998386642</v>
+        <v>-31.78473394289578</v>
       </c>
       <c r="F30">
-        <v>6.135517568744356</v>
+        <v>3.806315762287511</v>
       </c>
       <c r="G30">
-        <v>-7.249509915111783</v>
+        <v>-9.560972537177397</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-20.29979895291529</v>
       </c>
       <c r="E31">
-        <v>-25.41714475004532</v>
+        <v>-31.8754302203214</v>
       </c>
       <c r="F31">
-        <v>5.529674501358881</v>
+        <v>3.690443729983917</v>
       </c>
       <c r="G31">
-        <v>-7.371010246948575</v>
+        <v>-9.778488621289672</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-19.93168869548504</v>
       </c>
       <c r="E32">
-        <v>-25.41356725557926</v>
+        <v>-31.43830341707199</v>
       </c>
       <c r="F32">
-        <v>5.386514390072265</v>
+        <v>4.003526846606795</v>
       </c>
       <c r="G32">
-        <v>-7.815345048138474</v>
+        <v>-9.82710067198833</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-19.5638659120214</v>
       </c>
       <c r="E33">
-        <v>-25.2105602942894</v>
+        <v>-31.16464773278847</v>
       </c>
       <c r="F33">
-        <v>6.030734062494635</v>
+        <v>3.579951115594102</v>
       </c>
       <c r="G33">
-        <v>-6.998563942143948</v>
+        <v>-10.39830219933418</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-19.20111855519277</v>
       </c>
       <c r="E34">
-        <v>-24.75768572267832</v>
+        <v>-30.86255323173678</v>
       </c>
       <c r="F34">
-        <v>5.452840111279616</v>
+        <v>3.556669021371019</v>
       </c>
       <c r="G34">
-        <v>-6.649599336849372</v>
+        <v>-10.27160100045519</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-18.85410656087067</v>
       </c>
       <c r="E35">
-        <v>-24.1810434279636</v>
+        <v>-30.35316783298398</v>
       </c>
       <c r="F35">
-        <v>4.74051207099907</v>
+        <v>3.671489027073058</v>
       </c>
       <c r="G35">
-        <v>-6.708623053269038</v>
+        <v>-10.09986976115104</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-18.54350340574869</v>
       </c>
       <c r="E36">
-        <v>-23.50573474156976</v>
+        <v>-30.60875037750289</v>
       </c>
       <c r="F36">
-        <v>5.603500261031178</v>
+        <v>3.5709848668262</v>
       </c>
       <c r="G36">
-        <v>-6.811878968638907</v>
+        <v>-9.944135077892645</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-18.28052449707997</v>
       </c>
       <c r="E37">
-        <v>-22.79247744299164</v>
+        <v>-29.15636913681484</v>
       </c>
       <c r="F37">
-        <v>5.584626738125795</v>
+        <v>3.524631083700345</v>
       </c>
       <c r="G37">
-        <v>-6.37734007169971</v>
+        <v>-10.27283583394134</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-18.05239581359358</v>
       </c>
       <c r="E38">
-        <v>-23.33180964035716</v>
+        <v>-28.98799141626164</v>
       </c>
       <c r="F38">
-        <v>5.696870521205128</v>
+        <v>3.628394041309817</v>
       </c>
       <c r="G38">
-        <v>-7.770722204814638</v>
+        <v>-9.549322727424702</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.85525301234002</v>
       </c>
       <c r="E39">
-        <v>-21.67769846804942</v>
+        <v>-29.22991155469941</v>
       </c>
       <c r="F39">
-        <v>5.635140582348509</v>
+        <v>3.876017909028673</v>
       </c>
       <c r="G39">
-        <v>-6.40695621209403</v>
+        <v>-9.637797056961723</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.69894043557803</v>
       </c>
       <c r="E40">
-        <v>-22.32978966820594</v>
+        <v>-28.83882348244898</v>
       </c>
       <c r="F40">
-        <v>5.271850117441952</v>
+        <v>3.861741825208826</v>
       </c>
       <c r="G40">
-        <v>-7.946442651493614</v>
+        <v>-10.25626655351729</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.57402698282132</v>
       </c>
       <c r="E41">
-        <v>-21.92242173189793</v>
+        <v>-28.56312998486201</v>
       </c>
       <c r="F41">
-        <v>5.139516768109925</v>
+        <v>3.893001097520869</v>
       </c>
       <c r="G41">
-        <v>-7.457590944437134</v>
+        <v>-9.456451993411527</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.46205567727956</v>
       </c>
       <c r="E42">
-        <v>-21.41214875223963</v>
+        <v>-27.06905508398533</v>
       </c>
       <c r="F42">
-        <v>6.022599494599143</v>
+        <v>4.021121370242256</v>
       </c>
       <c r="G42">
-        <v>-6.738411342031401</v>
+        <v>-9.749124082356335</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.35456358201856</v>
       </c>
       <c r="E43">
-        <v>-21.17447179394705</v>
+        <v>-27.36439310181758</v>
       </c>
       <c r="F43">
-        <v>5.796281236480291</v>
+        <v>3.815127934718492</v>
       </c>
       <c r="G43">
-        <v>-7.190065759408629</v>
+        <v>-10.04373615098716</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-17.26079742925635</v>
       </c>
       <c r="E44">
-        <v>-18.66403977221087</v>
+        <v>-26.23368295531638</v>
       </c>
       <c r="F44">
-        <v>5.594111544887849</v>
+        <v>3.733550312890797</v>
       </c>
       <c r="G44">
-        <v>-6.924295163515938</v>
+        <v>-9.922014012599234</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-17.1670976161547</v>
       </c>
       <c r="E45">
-        <v>-18.84693578043266</v>
+        <v>-25.96848646047918</v>
       </c>
       <c r="F45">
-        <v>5.815641839418521</v>
+        <v>3.774597574434318</v>
       </c>
       <c r="G45">
-        <v>-7.813160088082555</v>
+        <v>-10.29705247456111</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-17.06465191119185</v>
       </c>
       <c r="E46">
-        <v>-17.04198113892941</v>
+        <v>-24.78511921821679</v>
       </c>
       <c r="F46">
-        <v>5.955821484789865</v>
+        <v>3.818388388815911</v>
       </c>
       <c r="G46">
-        <v>-7.503905476531537</v>
+        <v>-10.46061659801988</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-16.96044379934754</v>
       </c>
       <c r="E47">
-        <v>-16.71762918813002</v>
+        <v>-24.64251304324124</v>
       </c>
       <c r="F47">
-        <v>5.910862672370324</v>
+        <v>3.775437538980757</v>
       </c>
       <c r="G47">
-        <v>-7.761422882394825</v>
+        <v>-10.69509260692984</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-16.86838248454597</v>
       </c>
       <c r="E48">
-        <v>-17.11727607625495</v>
+        <v>-24.66024654745528</v>
       </c>
       <c r="F48">
-        <v>5.673759070667022</v>
+        <v>3.937611995631233</v>
       </c>
       <c r="G48">
-        <v>-7.827160385168133</v>
+        <v>-10.31500225247504</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-16.77961201242812</v>
       </c>
       <c r="E49">
-        <v>-17.80612942840573</v>
+        <v>-24.39709239439555</v>
       </c>
       <c r="F49">
-        <v>5.690006668905531</v>
+        <v>3.647242713193117</v>
       </c>
       <c r="G49">
-        <v>-8.636939687347102</v>
+        <v>-10.1666236014049</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-16.69869608143456</v>
       </c>
       <c r="E50">
-        <v>-15.92089399969451</v>
+        <v>-23.72430153954997</v>
       </c>
       <c r="F50">
-        <v>5.92806786332647</v>
+        <v>3.758273766394751</v>
       </c>
       <c r="G50">
-        <v>-9.312797490825933</v>
+        <v>-10.92932032492436</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-16.64233125905785</v>
       </c>
       <c r="E51">
-        <v>-14.65448360107945</v>
+        <v>-22.86071248933921</v>
       </c>
       <c r="F51">
-        <v>5.323396107448554</v>
+        <v>3.950677006308187</v>
       </c>
       <c r="G51">
-        <v>-7.891937829735053</v>
+        <v>-11.01404711691092</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-16.62108761434408</v>
       </c>
       <c r="E52">
-        <v>-15.85257744081479</v>
+        <v>-22.8507272041523</v>
       </c>
       <c r="F52">
-        <v>5.693731008748518</v>
+        <v>3.762223422171299</v>
       </c>
       <c r="G52">
-        <v>-9.967004326477928</v>
+        <v>-10.3440655317643</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-16.62664910249579</v>
       </c>
       <c r="E53">
-        <v>-13.99553629127533</v>
+        <v>-23.20270284639848</v>
       </c>
       <c r="F53">
-        <v>5.959739662605106</v>
+        <v>3.723845160399598</v>
       </c>
       <c r="G53">
-        <v>-7.859550762724362</v>
+        <v>-11.3232057226413</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-16.66327243704205</v>
       </c>
       <c r="E54">
-        <v>-15.19887410391155</v>
+        <v>-22.57169169274767</v>
       </c>
       <c r="F54">
-        <v>6.176551576409432</v>
+        <v>3.812944358244713</v>
       </c>
       <c r="G54">
-        <v>-9.071534863560466</v>
+        <v>-11.04666261156382</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-16.74624140370597</v>
       </c>
       <c r="E55">
-        <v>-13.98182860045411</v>
+        <v>-22.10452525716838</v>
       </c>
       <c r="F55">
-        <v>5.595771593163059</v>
+        <v>3.858728224597442</v>
       </c>
       <c r="G55">
-        <v>-9.733819430328284</v>
+        <v>-11.18689401006181</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-16.87039534530722</v>
       </c>
       <c r="E56">
-        <v>-14.79169636351187</v>
+        <v>-21.81363872928567</v>
       </c>
       <c r="F56">
-        <v>5.808791240997369</v>
+        <v>3.720110880147778</v>
       </c>
       <c r="G56">
-        <v>-9.517250162240241</v>
+        <v>-11.11982235743618</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-17.02215677973221</v>
       </c>
       <c r="E57">
-        <v>-13.32163596029787</v>
+        <v>-20.88130744363849</v>
       </c>
       <c r="F57">
-        <v>5.849419348635074</v>
+        <v>3.514932558148368</v>
       </c>
       <c r="G57">
-        <v>-8.870578128235627</v>
+        <v>-11.4517873113866</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-17.19821344984755</v>
       </c>
       <c r="E58">
-        <v>-11.46460386770642</v>
+        <v>-21.47368618552986</v>
       </c>
       <c r="F58">
-        <v>5.431643846176782</v>
+        <v>3.797054614724213</v>
       </c>
       <c r="G58">
-        <v>-8.962131265124171</v>
+        <v>-11.73233618256659</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-17.40509806321535</v>
       </c>
       <c r="E59">
-        <v>-12.24540788458295</v>
+        <v>-20.55402104168213</v>
       </c>
       <c r="F59">
-        <v>5.268859711117845</v>
+        <v>3.832018346061574</v>
       </c>
       <c r="G59">
-        <v>-8.770612895131793</v>
+        <v>-11.5795180899283</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-17.62414835461127</v>
       </c>
       <c r="E60">
-        <v>-12.99955730345033</v>
+        <v>-20.49541353107486</v>
       </c>
       <c r="F60">
-        <v>5.531796778644853</v>
+        <v>3.739554319826288</v>
       </c>
       <c r="G60">
-        <v>-9.207184467032103</v>
+        <v>-11.23868418447817</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-17.8408215948272</v>
       </c>
       <c r="E61">
-        <v>-13.30962644722953</v>
+        <v>-20.83511248028624</v>
       </c>
       <c r="F61">
-        <v>6.131408866426471</v>
+        <v>3.566925866552482</v>
       </c>
       <c r="G61">
-        <v>-9.616589702237153</v>
+        <v>-11.73382923860481</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-18.05383583142801</v>
       </c>
       <c r="E62">
-        <v>-12.80191205538556</v>
+        <v>-20.22085668046381</v>
       </c>
       <c r="F62">
-        <v>5.247650192136567</v>
+        <v>3.837661184809445</v>
       </c>
       <c r="G62">
-        <v>-9.486478641452717</v>
+        <v>-12.28174438862742</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-18.26432340916796</v>
       </c>
       <c r="E63">
-        <v>-12.59811713961837</v>
+        <v>-19.80618431558144</v>
       </c>
       <c r="F63">
-        <v>5.7040524665874</v>
+        <v>3.652893835615015</v>
       </c>
       <c r="G63">
-        <v>-9.265529521616218</v>
+        <v>-11.64298124791612</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-18.45015283725902</v>
       </c>
       <c r="E64">
-        <v>-12.27166397687942</v>
+        <v>-19.49142367273029</v>
       </c>
       <c r="F64">
-        <v>5.749234938205696</v>
+        <v>3.412102342234449</v>
       </c>
       <c r="G64">
-        <v>-10.37802510790614</v>
+        <v>-12.14418460037963</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-18.60616039469109</v>
       </c>
       <c r="E65">
-        <v>-13.28737352595583</v>
+        <v>-19.84383857695521</v>
       </c>
       <c r="F65">
-        <v>6.185938635817956</v>
+        <v>3.476087097161488</v>
       </c>
       <c r="G65">
-        <v>-10.24851325586432</v>
+        <v>-12.19733209846708</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.73816877679664</v>
       </c>
       <c r="E66">
-        <v>-11.89068345861411</v>
+        <v>-19.76345363484506</v>
       </c>
       <c r="F66">
-        <v>5.98786273593015</v>
+        <v>3.534440610484297</v>
       </c>
       <c r="G66">
-        <v>-10.90853340948327</v>
+        <v>-12.01921481681768</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.84594907214483</v>
       </c>
       <c r="E67">
-        <v>-12.23948011210691</v>
+        <v>-20.53448067633903</v>
       </c>
       <c r="F67">
-        <v>5.577406687842994</v>
+        <v>3.563264482632108</v>
       </c>
       <c r="G67">
-        <v>-10.39697798111847</v>
+        <v>-11.83420497935551</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.91477114506599</v>
       </c>
       <c r="E68">
-        <v>-10.28542093542711</v>
+        <v>-19.6129905574662</v>
       </c>
       <c r="F68">
-        <v>5.758756193133474</v>
+        <v>3.25986332421315</v>
       </c>
       <c r="G68">
-        <v>-8.866426704129379</v>
+        <v>-12.1748170782545</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.94445982787863</v>
       </c>
       <c r="E69">
-        <v>-11.51376498153368</v>
+        <v>-19.28446335363174</v>
       </c>
       <c r="F69">
-        <v>5.557782664070674</v>
+        <v>3.216258064129784</v>
       </c>
       <c r="G69">
-        <v>-9.755847800346595</v>
+        <v>-11.6980521729619</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.94935754446449</v>
       </c>
       <c r="E70">
-        <v>-11.60091999228531</v>
+        <v>-19.50753145477558</v>
       </c>
       <c r="F70">
-        <v>6.01618627416667</v>
+        <v>3.564263493719884</v>
       </c>
       <c r="G70">
-        <v>-10.49824756916478</v>
+        <v>-11.58930075199684</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.92590017824426</v>
       </c>
       <c r="E71">
-        <v>-12.94804591161308</v>
+        <v>-19.61324415201063</v>
       </c>
       <c r="F71">
-        <v>5.873775007012185</v>
+        <v>3.523893836711853</v>
       </c>
       <c r="G71">
-        <v>-8.676255726171487</v>
+        <v>-11.666068992507</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.86651145359468</v>
       </c>
       <c r="E72">
-        <v>-13.04641342400769</v>
+        <v>-19.30269498998662</v>
       </c>
       <c r="F72">
-        <v>5.347920752775836</v>
+        <v>3.41802351242966</v>
       </c>
       <c r="G72">
-        <v>-9.553497325349722</v>
+        <v>-11.5011111293762</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.77528695324821</v>
       </c>
       <c r="E73">
-        <v>-12.69284828738482</v>
+        <v>-19.6638770198904</v>
       </c>
       <c r="F73">
-        <v>5.53915765138613</v>
+        <v>3.069913708546807</v>
       </c>
       <c r="G73">
-        <v>-9.906864956211528</v>
+        <v>-11.73856993981704</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.66806591184106</v>
       </c>
       <c r="E74">
-        <v>-12.93839120502873</v>
+        <v>-19.39192404183376</v>
       </c>
       <c r="F74">
-        <v>5.878731957550537</v>
+        <v>3.306957667797108</v>
       </c>
       <c r="G74">
-        <v>-9.951640084630171</v>
+        <v>-12.13400136230083</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.53718016262104</v>
       </c>
       <c r="E75">
-        <v>-11.09648421562289</v>
+        <v>-20.27041177152975</v>
       </c>
       <c r="F75">
-        <v>5.928790199701711</v>
+        <v>3.159990379927225</v>
       </c>
       <c r="G75">
-        <v>-9.053399695096338</v>
+        <v>-11.89552952492497</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.37987476658644</v>
       </c>
       <c r="E76">
-        <v>-13.56936613088748</v>
+        <v>-19.57291809097233</v>
       </c>
       <c r="F76">
-        <v>5.363894989771421</v>
+        <v>3.125898091097609</v>
       </c>
       <c r="G76">
-        <v>-9.019016369125467</v>
+        <v>-11.58419589077529</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.20618714972853</v>
       </c>
       <c r="E77">
-        <v>-13.2292007488533</v>
+        <v>-20.4319741387014</v>
       </c>
       <c r="F77">
-        <v>5.089602661886838</v>
+        <v>3.176415248789934</v>
       </c>
       <c r="G77">
-        <v>-8.59616038739436</v>
+        <v>-11.37643267382171</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-18.02845869589276</v>
       </c>
       <c r="E78">
-        <v>-12.07330775839544</v>
+        <v>-20.58329309766771</v>
       </c>
       <c r="F78">
-        <v>5.115567009760186</v>
+        <v>2.943586022885077</v>
       </c>
       <c r="G78">
-        <v>-9.568765561376841</v>
+        <v>-11.23652239824103</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.83610021606965</v>
       </c>
       <c r="E79">
-        <v>-14.7342707846206</v>
+        <v>-20.91920624260868</v>
       </c>
       <c r="F79">
-        <v>5.022670575740638</v>
+        <v>2.926596207453659</v>
       </c>
       <c r="G79">
-        <v>-9.716379476427404</v>
+        <v>-11.21763573593948</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.63218863925277</v>
       </c>
       <c r="E80">
-        <v>-15.02171567225747</v>
+        <v>-21.24824969248002</v>
       </c>
       <c r="F80">
-        <v>5.14569970240442</v>
+        <v>2.787279720916032</v>
       </c>
       <c r="G80">
-        <v>-8.303213523169791</v>
+        <v>-10.61474897723727</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.43132131945553</v>
       </c>
       <c r="E81">
-        <v>-14.76856491828068</v>
+        <v>-22.2077337082772</v>
       </c>
       <c r="F81">
-        <v>5.23699573060176</v>
+        <v>2.86432782978522</v>
       </c>
       <c r="G81">
-        <v>-8.73351823236426</v>
+        <v>-11.08264493103016</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.23895354189829</v>
       </c>
       <c r="E82">
-        <v>-14.92972425126566</v>
+        <v>-22.80618060533885</v>
       </c>
       <c r="F82">
-        <v>5.586251994970088</v>
+        <v>2.748873294652636</v>
       </c>
       <c r="G82">
-        <v>-8.396772850655134</v>
+        <v>-10.86360599596982</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-17.04698228723552</v>
       </c>
       <c r="E83">
-        <v>-16.08709352425002</v>
+        <v>-23.80318755676359</v>
       </c>
       <c r="F83">
-        <v>4.987332422337212</v>
+        <v>2.656815168444721</v>
       </c>
       <c r="G83">
-        <v>-8.097304211718201</v>
+        <v>-10.45585934407995</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.85793250448559</v>
       </c>
       <c r="E84">
-        <v>-17.63514330682411</v>
+        <v>-24.51920269601237</v>
       </c>
       <c r="F84">
-        <v>4.842089795399957</v>
+        <v>2.720389053139972</v>
       </c>
       <c r="G84">
-        <v>-6.799242616315508</v>
+        <v>-10.46883337204835</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.69234205227333</v>
       </c>
       <c r="E85">
-        <v>-17.50804715532484</v>
+        <v>-24.8883276693256</v>
       </c>
       <c r="F85">
-        <v>4.985248249951768</v>
+        <v>2.636021489899648</v>
       </c>
       <c r="G85">
-        <v>-7.07622934049525</v>
+        <v>-10.13997702035931</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.54992914735953</v>
       </c>
       <c r="E86">
-        <v>-18.84211295561449</v>
+        <v>-25.50723421195391</v>
       </c>
       <c r="F86">
-        <v>4.638077814703689</v>
+        <v>2.863956721188766</v>
       </c>
       <c r="G86">
-        <v>-8.163770034510149</v>
+        <v>-10.47586497077376</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-16.42747828080639</v>
       </c>
       <c r="E87">
-        <v>-20.27520742550387</v>
+        <v>-27.00231443406029</v>
       </c>
       <c r="F87">
-        <v>5.130567086690079</v>
+        <v>2.819130447553673</v>
       </c>
       <c r="G87">
-        <v>-6.805919986668219</v>
+        <v>-10.15902589939228</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-16.33407724209347</v>
       </c>
       <c r="E88">
-        <v>-22.37210372933361</v>
+        <v>-28.03928064012871</v>
       </c>
       <c r="F88">
-        <v>5.385460706735904</v>
+        <v>2.473747629160836</v>
       </c>
       <c r="G88">
-        <v>-7.009991945345512</v>
+        <v>-9.898793846186786</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.289303960919</v>
       </c>
       <c r="E89">
-        <v>-23.59167159281332</v>
+        <v>-29.1208659005947</v>
       </c>
       <c r="F89">
-        <v>5.249939799637905</v>
+        <v>2.375145400470806</v>
       </c>
       <c r="G89">
-        <v>-7.400209258604947</v>
+        <v>-9.526556105751133</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.28738998474138</v>
       </c>
       <c r="E90">
-        <v>-24.75217456981099</v>
+        <v>-30.41525094739214</v>
       </c>
       <c r="F90">
-        <v>4.670672415269045</v>
+        <v>2.583764760661444</v>
       </c>
       <c r="G90">
-        <v>-6.499247600637832</v>
+        <v>-10.41720872490896</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.32933903286482</v>
       </c>
       <c r="E91">
-        <v>-26.1046984301559</v>
+        <v>-32.39352161035395</v>
       </c>
       <c r="F91">
-        <v>4.331558681380594</v>
+        <v>2.199725349049566</v>
       </c>
       <c r="G91">
-        <v>-6.890805684840671</v>
+        <v>-9.707497282745539</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.42802982311492</v>
       </c>
       <c r="E92">
-        <v>-29.59115698323928</v>
+        <v>-33.64845685583357</v>
       </c>
       <c r="F92">
-        <v>5.083681491691627</v>
+        <v>2.043924351196229</v>
       </c>
       <c r="G92">
-        <v>-7.170861284735317</v>
+        <v>-9.951947965365324</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.59457034395449</v>
       </c>
       <c r="E93">
-        <v>-29.98653804884898</v>
+        <v>-34.91691638893709</v>
       </c>
       <c r="F93">
-        <v>4.915062336647371</v>
+        <v>2.015768143175074</v>
       </c>
       <c r="G93">
-        <v>-6.179280063721732</v>
+        <v>-9.505322266662247</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.81202930326819</v>
       </c>
       <c r="E94">
-        <v>-31.42590445523899</v>
+        <v>-36.28576539807965</v>
       </c>
       <c r="F94">
-        <v>4.310441939548429</v>
+        <v>1.72591741873111</v>
       </c>
       <c r="G94">
-        <v>-6.030739195920174</v>
+        <v>-9.022442783758613</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.0801594292828</v>
       </c>
       <c r="E95">
-        <v>-34.40507429303513</v>
+        <v>-38.34071671141334</v>
       </c>
       <c r="F95">
-        <v>3.956591549564175</v>
+        <v>1.552230311916526</v>
       </c>
       <c r="G95">
-        <v>-5.578538538528965</v>
+        <v>-9.632112850270795</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.40968348659359</v>
       </c>
       <c r="E96">
-        <v>-37.04505010647173</v>
+        <v>-40.47756321293875</v>
       </c>
       <c r="F96">
-        <v>4.11302542011325</v>
+        <v>1.3665467883746</v>
       </c>
       <c r="G96">
-        <v>-5.784457781617173</v>
+        <v>-9.592601489259593</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.78963140287939</v>
       </c>
       <c r="E97">
-        <v>-39.45698329006708</v>
+        <v>-41.82516688627432</v>
       </c>
       <c r="F97">
-        <v>3.794965472134352</v>
+        <v>1.04287879307875</v>
       </c>
       <c r="G97">
-        <v>-6.188271505406393</v>
+        <v>-9.540188932281852</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.2106045438729</v>
       </c>
       <c r="E98">
-        <v>-40.37710807402659</v>
+        <v>-44.38060288269874</v>
       </c>
       <c r="F98">
-        <v>2.742368953805854</v>
+        <v>1.015425040615168</v>
       </c>
       <c r="G98">
-        <v>-5.549951977797359</v>
+        <v>-9.182332201668794</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.65047521364013</v>
       </c>
       <c r="E99">
-        <v>-43.5379829313805</v>
+        <v>-45.799455301834</v>
       </c>
       <c r="F99">
-        <v>3.145204021787254</v>
+        <v>0.8854011796021466</v>
       </c>
       <c r="G99">
-        <v>-6.110970267064411</v>
+        <v>-9.664142378363245</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-19.14072715520813</v>
       </c>
       <c r="E100">
-        <v>-45.39452368454212</v>
+        <v>-47.69185704066236</v>
       </c>
       <c r="F100">
-        <v>2.564520129159606</v>
+        <v>0.875016765840652</v>
       </c>
       <c r="G100">
-        <v>-6.576800440440799</v>
+        <v>-9.396163648595859</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.626297090004</v>
       </c>
       <c r="E101">
-        <v>-48.09886043481275</v>
+        <v>-49.85638383955965</v>
       </c>
       <c r="F101">
-        <v>2.525513964896583</v>
+        <v>0.07085011671393396</v>
       </c>
       <c r="G101">
-        <v>-6.251810805941625</v>
+        <v>-9.801281727327552</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-20.15690714040798</v>
       </c>
       <c r="E102">
-        <v>-50.9011016610107</v>
+        <v>-52.09924644607862</v>
       </c>
       <c r="F102">
-        <v>2.569395899692484</v>
+        <v>0.2413181878012386</v>
       </c>
       <c r="G102">
-        <v>-5.776224454861005</v>
+        <v>-9.928502681856205</v>
       </c>
     </row>
   </sheetData>
